--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Fiets.xlsx
@@ -388,10 +388,10 @@
         <v>0.4215077612063589</v>
       </c>
       <c r="C2">
-        <v>0.58792005918047</v>
+        <v>0.5879200591804699</v>
       </c>
       <c r="D2">
-        <v>0.672081007344369</v>
+        <v>0.6720810073443689</v>
       </c>
       <c r="E2">
         <v>0.7325767622515603</v>
@@ -408,7 +408,7 @@
         <v>0.6195689296840667</v>
       </c>
       <c r="D3">
-        <v>0.7015778299709426</v>
+        <v>0.7015778299709424</v>
       </c>
       <c r="E3">
         <v>0.7565117611137623</v>
@@ -419,13 +419,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.3758487441489632</v>
+        <v>0.3758487441489631</v>
       </c>
       <c r="C4">
         <v>0.5318206555514727</v>
       </c>
       <c r="D4">
-        <v>0.6168906973569016</v>
+        <v>0.6168906973569015</v>
       </c>
       <c r="E4">
         <v>0.6837215924857288</v>
@@ -439,7 +439,7 @@
         <v>0.4865354429621429</v>
       </c>
       <c r="C5">
-        <v>0.6651261304297056</v>
+        <v>0.6651261304297055</v>
       </c>
       <c r="D5">
         <v>0.7373143177077819</v>
@@ -456,7 +456,7 @@
         <v>0.4768322874951845</v>
       </c>
       <c r="C6">
-        <v>0.6534093172196863</v>
+        <v>0.6534093172196862</v>
       </c>
       <c r="D6">
         <v>0.7264082756098442</v>
@@ -470,10 +470,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.5011393183364669</v>
+        <v>0.5011393183364667</v>
       </c>
       <c r="C7">
-        <v>0.6810079994693606</v>
+        <v>0.6810079994693605</v>
       </c>
       <c r="D7">
         <v>0.7581868676151399</v>
@@ -490,10 +490,10 @@
         <v>0.435592459430847</v>
       </c>
       <c r="C8">
-        <v>0.6067621287882927</v>
+        <v>0.6067621287882924</v>
       </c>
       <c r="D8">
-        <v>0.6972172193191215</v>
+        <v>0.6972172193191213</v>
       </c>
       <c r="E8">
         <v>0.7449368387269226</v>
@@ -524,7 +524,7 @@
         <v>0.5196008561227122</v>
       </c>
       <c r="C10">
-        <v>0.6962885743215873</v>
+        <v>0.6962885743215872</v>
       </c>
       <c r="D10">
         <v>0.7614197283363611</v>
@@ -538,13 +538,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.514738428575523</v>
+        <v>0.5147384285755229</v>
       </c>
       <c r="C11">
-        <v>0.6892710809081366</v>
+        <v>0.6892710809081365</v>
       </c>
       <c r="D11">
-        <v>0.7536675349904853</v>
+        <v>0.7536675349904851</v>
       </c>
       <c r="E11">
         <v>0.7824232959475607</v>
@@ -558,7 +558,7 @@
         <v>0.4804581224628028</v>
       </c>
       <c r="C12">
-        <v>0.6241881254001516</v>
+        <v>0.6241881254001515</v>
       </c>
       <c r="D12">
         <v>0.659795161260209</v>
@@ -578,7 +578,7 @@
         <v>0.6925478065089196</v>
       </c>
       <c r="D13">
-        <v>0.7569554584173224</v>
+        <v>0.7569554584173221</v>
       </c>
       <c r="E13">
         <v>0.7853295825320202</v>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.4215077612063589</v>
+        <v>1.424292393106278</v>
       </c>
       <c r="C2">
-        <v>0.5879200591804699</v>
+        <v>0.9348736580360384</v>
       </c>
       <c r="D2">
-        <v>0.6720810073443689</v>
+        <v>0.550543004818621</v>
       </c>
       <c r="E2">
-        <v>0.7325767622515603</v>
+        <v>0.3941701649633306</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.4480068978269227</v>
+        <v>0.8492068557177033</v>
       </c>
       <c r="C3">
-        <v>0.6195689296840667</v>
+        <v>0.6361473297347028</v>
       </c>
       <c r="D3">
-        <v>0.7015778299709424</v>
+        <v>0.5926532590853557</v>
       </c>
       <c r="E3">
-        <v>0.7565117611137623</v>
+        <v>0.5759350230230638</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.3758487441489631</v>
+        <v>0.916807182218804</v>
       </c>
       <c r="C4">
-        <v>0.5318206555514727</v>
+        <v>0.6896874185678047</v>
       </c>
       <c r="D4">
-        <v>0.6168906973569015</v>
+        <v>0.5015934652661029</v>
       </c>
       <c r="E4">
-        <v>0.6837215924857288</v>
+        <v>0.4306726325720635</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.4865354429621429</v>
+        <v>0.1212572853202864</v>
       </c>
       <c r="C5">
-        <v>0.6651261304297055</v>
+        <v>0.1667963361139509</v>
       </c>
       <c r="D5">
-        <v>0.7373143177077819</v>
+        <v>0.1837579027104534</v>
       </c>
       <c r="E5">
-        <v>0.7920320214721451</v>
+        <v>0.1986210332484327</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.4768322874951845</v>
+        <v>0.5249365371640472</v>
       </c>
       <c r="C6">
-        <v>0.6534093172196862</v>
+        <v>0.5660279443159711</v>
       </c>
       <c r="D6">
-        <v>0.7264082756098442</v>
+        <v>0.6854489898666445</v>
       </c>
       <c r="E6">
-        <v>0.7829951580196046</v>
+        <v>0.8931737198120534</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.5011393183364667</v>
+        <v>0.9521647048392868</v>
       </c>
       <c r="C7">
-        <v>0.6810079994693605</v>
+        <v>0.6469575994958926</v>
       </c>
       <c r="D7">
-        <v>0.7581868676151399</v>
+        <v>0.6547977493039842</v>
       </c>
       <c r="E7">
-        <v>0.8015667912701183</v>
+        <v>0.6345737097555103</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.435592459430847</v>
+        <v>0.1088650452813808</v>
       </c>
       <c r="C8">
-        <v>0.6067621287882924</v>
+        <v>0.1518287258188743</v>
       </c>
       <c r="D8">
-        <v>0.6972172193191213</v>
+        <v>0.174251373063965</v>
       </c>
       <c r="E8">
-        <v>0.7449368387269226</v>
+        <v>0.1861776551084899</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.504913894623724</v>
+        <v>0.9376146280210786</v>
       </c>
       <c r="C9">
-        <v>0.687597352504432</v>
+        <v>0.8005554229795351</v>
       </c>
       <c r="D9">
-        <v>0.7652800459638724</v>
+        <v>0.6556239312220005</v>
       </c>
       <c r="E9">
-        <v>0.8082516464155737</v>
+        <v>0.5636679019934275</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.5196008561227122</v>
+        <v>0.1306510823198727</v>
       </c>
       <c r="C10">
-        <v>0.6962885743215872</v>
+        <v>0.1730659462186604</v>
       </c>
       <c r="D10">
-        <v>0.7614197283363611</v>
+        <v>0.1914552496105879</v>
       </c>
       <c r="E10">
-        <v>0.7901193396688405</v>
+        <v>0.1963880439639315</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.5147384285755229</v>
+        <v>0.1328357235033607</v>
       </c>
       <c r="C11">
-        <v>0.6892710809081365</v>
+        <v>0.166759132477775</v>
       </c>
       <c r="D11">
-        <v>0.7536675349904851</v>
+        <v>0.1823389197557625</v>
       </c>
       <c r="E11">
-        <v>0.7824232959475607</v>
+        <v>0.2019156892767898</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.4804581224628028</v>
+        <v>0.4468942354954813</v>
       </c>
       <c r="C12">
-        <v>0.6241881254001515</v>
+        <v>0.5341390823245975</v>
       </c>
       <c r="D12">
-        <v>0.659795161260209</v>
+        <v>0.6670383477510234</v>
       </c>
       <c r="E12">
-        <v>0.6650539704803021</v>
+        <v>0.8714905854795397</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.517283874555091</v>
+        <v>0.1299841530933305</v>
       </c>
       <c r="C13">
-        <v>0.6925478065089196</v>
+        <v>0.1704733062175802</v>
       </c>
       <c r="D13">
-        <v>0.7569554584173221</v>
+        <v>0.1902093203202502</v>
       </c>
       <c r="E13">
-        <v>0.7853295825320202</v>
+        <v>0.197339228431123</v>
       </c>
     </row>
   </sheetData>
